--- a/jigyosho/izumo_kaigo_list.xlsx
+++ b/jigyosho/izumo_kaigo_list.xlsx
@@ -2673,11 +2673,7 @@
           <t>https://mandanosato.jp/</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>https://mandanosato.jp/pages/84/</t>
-        </is>
-      </c>
+      <c r="K3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -3393,11 +3389,7 @@
           <t>https://mandanosato.jp/</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>https://mandanosato.jp/pages/84/</t>
-        </is>
-      </c>
+      <c r="K19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -4308,34 +4300,32 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8105,11 +8095,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="K43" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="K43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -8538,11 +8524,7 @@
           <t>https://mandanosato.jp/</t>
         </is>
       </c>
-      <c r="K52" s="8" t="inlineStr">
-        <is>
-          <t>https://mandanosato.jp/pages/84/</t>
-        </is>
-      </c>
+      <c r="K52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -8975,11 +8957,7 @@
           <t>https://care-service-izumo.biz</t>
         </is>
       </c>
-      <c r="K61" s="8" t="inlineStr">
-        <is>
-          <t>https://care-service-izumo.biz/info/6227529</t>
-        </is>
-      </c>
+      <c r="K61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -9181,21 +9159,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12320,11 +12295,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="L32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -13410,11 +13381,7 @@
           <t>https://care-service-izumo.biz</t>
         </is>
       </c>
-      <c r="L53" s="8" t="inlineStr">
-        <is>
-          <t>https://care-service-izumo.biz/info/6227529</t>
-        </is>
-      </c>
+      <c r="L53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -14930,11 +14897,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="L82" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="L82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -15872,11 +15835,7 @@
           <t>https://izumo-tokushuen.com/</t>
         </is>
       </c>
-      <c r="L100" s="8" t="inlineStr">
-        <is>
-          <t>https://izumo-tokushuen.com/price</t>
-        </is>
-      </c>
+      <c r="L100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
@@ -16034,11 +15993,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="L103" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="L103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -16144,11 +16099,7 @@
           <t>https://mandanosato.jp/pages/85/</t>
         </is>
       </c>
-      <c r="L105" s="8" t="inlineStr">
-        <is>
-          <t>https://mandanosato.jp/pages/84/</t>
-        </is>
-      </c>
+      <c r="L105" s="6" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -17764,11 +17715,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="L135" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="L135" s="6" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
@@ -17822,11 +17769,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="L136" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="L136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
@@ -17988,11 +17931,7 @@
           <t>https://mandanosato.jp/</t>
         </is>
       </c>
-      <c r="L139" s="8" t="inlineStr">
-        <is>
-          <t>https://mandanosato.jp/pages/84/</t>
-        </is>
-      </c>
+      <c r="L139" s="6" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
@@ -18576,11 +18515,7 @@
           <t>https://www.oomagari.com/</t>
         </is>
       </c>
-      <c r="L150" s="8" t="inlineStr">
-        <is>
-          <t>https://www.oomagari.com/fee.html</t>
-        </is>
-      </c>
+      <c r="L150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
@@ -18904,11 +18839,7 @@
           <t>https://mandanosato.jp/pages/85/</t>
         </is>
       </c>
-      <c r="L156" s="8" t="inlineStr">
-        <is>
-          <t>https://mandanosato.jp/pages/84/</t>
-        </is>
-      </c>
+      <c r="L156" s="6" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
@@ -21682,11 +21613,7 @@
           <t>https://mandanosato.jp/</t>
         </is>
       </c>
-      <c r="L210" s="8" t="inlineStr">
-        <is>
-          <t>https://mandanosato.jp/pages/84/</t>
-        </is>
-      </c>
+      <c r="L210" s="6" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
@@ -22482,11 +22409,7 @@
           <t>https://mandanosato.jp/</t>
         </is>
       </c>
-      <c r="L226" s="8" t="inlineStr">
-        <is>
-          <t>https://mandanosato.jp/pages/84/</t>
-        </is>
-      </c>
+      <c r="L226" s="6" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
@@ -27130,11 +27053,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="L316" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="L316" s="6" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="6" t="inlineStr">
@@ -27608,11 +27527,7 @@
           <t>https://mandanosato.jp/</t>
         </is>
       </c>
-      <c r="L325" s="8" t="inlineStr">
-        <is>
-          <t>https://mandanosato.jp/pages/84/</t>
-        </is>
-      </c>
+      <c r="L325" s="6" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="6" t="inlineStr">
@@ -28090,11 +28005,7 @@
           <t>https://care-service-izumo.biz</t>
         </is>
       </c>
-      <c r="L334" s="8" t="inlineStr">
-        <is>
-          <t>https://care-service-izumo.biz/info/6227529</t>
-        </is>
-      </c>
+      <c r="L334" s="6" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="6" t="inlineStr">
@@ -31188,11 +31099,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="L394" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="L394" s="6" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="6" t="inlineStr">
@@ -31242,11 +31149,7 @@
           <t>https://www.hikawa-hp.com/</t>
         </is>
       </c>
-      <c r="L395" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="L395" s="6" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="6" t="inlineStr">
@@ -31610,11 +31513,7 @@
           <t>https://care-service-izumo.biz/</t>
         </is>
       </c>
-      <c r="L402" s="8" t="inlineStr">
-        <is>
-          <t>https://care-service-izumo.biz/info/6227529</t>
-        </is>
-      </c>
+      <c r="L402" s="6" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="6" t="inlineStr">
@@ -33340,11 +33239,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="L434" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="L434" s="6" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="6" t="inlineStr">
@@ -33674,304 +33569,284 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K153" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K167" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K171" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K172" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K176" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K179" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K180" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K181" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K182" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K183" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K184" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K185" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K186" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K187" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K188" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K189" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K191" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K192" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K193" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K194" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K195" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K196" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K199" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K200" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K201" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K202" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K203" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K204" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K205" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K206" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K207" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K208" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K209" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K210" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L210" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K213" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K214" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K215" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K216" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K218" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K219" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K220" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K222" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K223" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K226" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L226" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K228" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K229" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K230" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K232" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K237" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L237" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K238" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K241" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K242" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L242" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K243" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K244" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K245" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K246" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K247" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K248" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K249" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K250" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K251" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K252" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L252" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K253" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K254" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K256" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K257" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K261" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K263" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K264" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K265" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K267" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K268" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K269" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K273" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K275" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K281" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K284" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K290" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K294" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K295" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K298" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K306" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K307" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K308" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K309" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K312" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K313" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K315" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K316" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L316" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K318" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K322" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K323" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K324" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K325" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L325" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K327" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K328" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K329" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K330" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K333" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K334" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L334" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K338" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K339" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K340" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K341" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K342" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K343" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K344" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K345" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L345" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K347" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K348" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K349" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K350" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L350" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K351" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L351" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K352" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K353" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K354" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K355" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K356" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K357" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L357" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K358" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K359" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K360" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L360" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K361" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K362" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K363" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K364" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K365" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K366" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K367" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K368" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K369" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K371" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K372" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K373" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K374" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K375" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K376" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K377" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K378" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K380" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K381" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K382" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K383" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K386" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K387" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K390" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K391" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L391" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K392" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L392" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K393" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K394" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L394" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K395" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L395" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K396" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K402" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L402" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K403" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K404" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K405" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K406" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K408" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K409" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K410" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K411" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K412" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K413" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K416" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K419" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K421" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K422" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K423" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K424" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K429" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L429" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K430" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L430" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K431" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K432" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K433" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K434" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L434" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K436" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K438" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K153" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K167" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K171" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K172" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K176" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K179" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K180" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K181" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K182" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K183" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K184" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K185" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K186" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K187" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K188" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K189" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K191" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K192" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K193" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K194" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K195" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K196" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K199" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K200" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K201" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K202" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K203" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K204" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K205" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K206" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K207" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K208" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K209" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K210" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K213" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K214" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K215" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K216" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K218" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K219" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K220" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K222" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K223" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K226" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K228" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K229" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K230" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K232" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K237" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L237" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K238" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K241" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K242" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L242" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K243" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K244" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K245" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K246" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K247" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K248" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K249" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K250" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K251" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K252" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L252" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K253" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K254" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K256" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K257" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K261" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K263" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K264" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K265" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K267" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K268" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K269" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K273" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K275" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K281" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K284" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K290" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K294" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K295" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K298" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K306" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K307" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K308" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K309" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K312" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K313" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K315" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K316" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K318" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K322" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K323" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K324" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K325" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K327" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K328" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K329" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K330" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K333" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K334" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K338" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K339" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K340" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K341" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K342" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K343" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K344" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K345" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L345" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K347" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K348" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K349" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K350" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L350" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K351" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L351" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K352" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K353" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K354" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K355" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K356" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K357" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L357" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K358" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K359" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K360" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L360" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K361" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K362" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K363" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K364" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K365" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K366" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K367" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K368" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K369" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K371" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K372" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K373" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K374" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K375" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K376" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K377" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K378" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K380" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K381" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K382" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K383" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K386" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K387" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K390" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K391" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L391" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K392" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L392" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K393" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K394" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K395" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K396" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K402" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K403" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K404" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K405" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K406" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K408" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K409" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K410" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K411" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K412" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K413" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K416" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K419" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K421" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K422" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K423" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K424" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K429" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L429" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K430" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L430" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K431" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K432" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K433" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K434" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K436" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K438" r:id="rId293"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35950,17 +35825,12 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="K4" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36095,16 +35965,11 @@
           <t>https://www.hikawa-hp.com/</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="K3" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36523,11 +36388,7 @@
           <t>https://care-service-izumo.biz/</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>https://care-service-izumo.biz/info/6227529</t>
-        </is>
-      </c>
+      <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -38093,11 +37954,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="K41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -38383,34 +38240,32 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39955,11 +39810,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="K33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -40940,11 +40791,7 @@
           <t>https://care-service-izumo.biz</t>
         </is>
       </c>
-      <c r="K54" s="8" t="inlineStr">
-        <is>
-          <t>https://care-service-izumo.biz/info/6227529</t>
-        </is>
-      </c>
+      <c r="K54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -41053,17 +40900,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42529,11 +42374,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="K26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -42961,8 +42802,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43489,11 +43329,7 @@
           <t>https://izumo-tokushuen.com/</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>https://izumo-tokushuen.com/price</t>
-        </is>
-      </c>
+      <c r="K11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -43636,11 +43472,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="K14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -43736,11 +43568,7 @@
           <t>https://mandanosato.jp/pages/85/</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>https://mandanosato.jp/pages/84/</t>
-        </is>
-      </c>
+      <c r="K16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -43899,15 +43727,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45316,11 +45141,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="K29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -45369,11 +45190,7 @@
           <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com/theme/hikawa_iryosekyo/pdf/low_price.pdf</t>
-        </is>
-      </c>
+      <c r="K30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -45520,11 +45337,7 @@
           <t>https://mandanosato.jp/</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t>https://mandanosato.jp/pages/84/</t>
-        </is>
-      </c>
+      <c r="K33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -45929,18 +45742,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46177,11 +45987,7 @@
           <t>https://www.oomagari.com/</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>https://www.oomagari.com/fee.html</t>
-        </is>
-      </c>
+      <c r="K5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -46475,11 +46281,7 @@
           <t>https://mandanosato.jp/pages/85/</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>https://mandanosato.jp/pages/84/</t>
-        </is>
-      </c>
+      <c r="K11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -46631,15 +46433,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jigyosho/izumo_kaigo_list.xlsx
+++ b/jigyosho/izumo_kaigo_list.xlsx
@@ -3796,7 +3796,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>平田</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>平田</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -19014,7 +19014,7 @@
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
@@ -22866,7 +22866,7 @@
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D236" s="7" t="inlineStr">
@@ -23942,7 +23942,7 @@
       </c>
       <c r="C257" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D257" s="7" t="inlineStr">
@@ -25342,7 +25342,7 @@
       </c>
       <c r="C284" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>平田</t>
         </is>
       </c>
       <c r="D284" s="7" t="inlineStr">
@@ -25598,7 +25598,7 @@
       </c>
       <c r="C289" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D289" s="7" t="inlineStr">
@@ -29816,7 +29816,7 @@
       </c>
       <c r="C370" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D370" s="7" t="inlineStr">
@@ -31528,7 +31528,7 @@
       </c>
       <c r="C403" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>平田</t>
         </is>
       </c>
       <c r="D403" s="7" t="inlineStr">
@@ -32124,7 +32124,7 @@
       </c>
       <c r="C414" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D414" s="7" t="inlineStr">
@@ -34457,7 +34457,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -36398,7 +36398,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>平田</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -36939,7 +36939,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -38500,7 +38500,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>平田</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -39530,7 +39530,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -46539,7 +46539,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">

--- a/jigyosho/izumo_kaigo_list.xlsx
+++ b/jigyosho/izumo_kaigo_list.xlsx
@@ -6327,9 +6327,7 @@
           <t>0853-20-0956</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>40</v>
-      </c>
+      <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="7" t="inlineStr">
         <is>
           <t>平日,祝日</t>
@@ -6374,9 +6372,7 @@
           <t>0853-23-7376</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>180</v>
-      </c>
+      <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -6515,9 +6511,7 @@
           <t>0853-53-3330</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>160</v>
-      </c>
+      <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -6611,9 +6605,7 @@
           <t>0853-25-7038</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>50</v>
-      </c>
+      <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -6793,9 +6785,7 @@
           <t>0853-25-8782</t>
         </is>
       </c>
-      <c r="F16" s="6" t="n">
-        <v>240</v>
-      </c>
+      <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -6840,9 +6830,7 @@
           <t>050-3535-6724</t>
         </is>
       </c>
-      <c r="F17" s="6" t="n">
-        <v>5</v>
-      </c>
+      <c r="F17" s="6" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -6891,9 +6879,7 @@
           <t>０８５３－２８－３６６７</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n">
-        <v>5</v>
-      </c>
+      <c r="F18" s="6" t="inlineStr"/>
       <c r="G18" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,日曜日,祝日</t>
@@ -6938,9 +6924,7 @@
           <t>0853-77-9841</t>
         </is>
       </c>
-      <c r="F19" s="6" t="n">
-        <v>80</v>
-      </c>
+      <c r="F19" s="6" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -7030,9 +7014,7 @@
           <t>0853-62-9114</t>
         </is>
       </c>
-      <c r="F21" s="6" t="n">
-        <v>40</v>
-      </c>
+      <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -7175,9 +7157,7 @@
           <t>0853-31-9447</t>
         </is>
       </c>
-      <c r="F24" s="6" t="n">
-        <v>35</v>
-      </c>
+      <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -7316,9 +7296,7 @@
           <t>0853-27-9737</t>
         </is>
       </c>
-      <c r="F27" s="6" t="n">
-        <v>59</v>
-      </c>
+      <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -7453,9 +7431,7 @@
           <t>0853－31－5988</t>
         </is>
       </c>
-      <c r="F30" s="6" t="n">
-        <v>50</v>
-      </c>
+      <c r="F30" s="6" t="inlineStr"/>
       <c r="G30" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -7500,9 +7476,7 @@
           <t>0853-20-7497</t>
         </is>
       </c>
-      <c r="F31" s="6" t="n">
-        <v>120</v>
-      </c>
+      <c r="F31" s="6" t="inlineStr"/>
       <c r="G31" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -7833,9 +7807,7 @@
           <t>0853-24-8515</t>
         </is>
       </c>
-      <c r="F38" s="6" t="n">
-        <v>20</v>
-      </c>
+      <c r="F38" s="6" t="inlineStr"/>
       <c r="G38" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -7929,9 +7901,7 @@
           <t>0853-72-5192</t>
         </is>
       </c>
-      <c r="F40" s="6" t="n">
-        <v>161</v>
-      </c>
+      <c r="F40" s="6" t="inlineStr"/>
       <c r="G40" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,祝日</t>
@@ -8217,9 +8187,7 @@
           <t>0853-24-9913</t>
         </is>
       </c>
-      <c r="F46" s="6" t="n">
-        <v>5</v>
-      </c>
+      <c r="F46" s="6" t="inlineStr"/>
       <c r="G46" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -8264,9 +8232,7 @@
           <t>０５０−３１７４−７１２２</t>
         </is>
       </c>
-      <c r="F47" s="6" t="n">
-        <v>5</v>
-      </c>
+      <c r="F47" s="6" t="inlineStr"/>
       <c r="G47" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -8793,9 +8759,7 @@
           <t>0853-21-2810</t>
         </is>
       </c>
-      <c r="F58" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="F58" s="6" t="inlineStr"/>
       <c r="G58" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -8840,9 +8804,7 @@
           <t>0853-21-2880</t>
         </is>
       </c>
-      <c r="F59" s="6" t="n">
-        <v>20</v>
-      </c>
+      <c r="F59" s="6" t="inlineStr"/>
       <c r="G59" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -25100,9 +25062,7 @@
           <t>0853-20-0956</t>
         </is>
       </c>
-      <c r="G279" s="6" t="n">
-        <v>40</v>
-      </c>
+      <c r="G279" s="6" t="inlineStr"/>
       <c r="H279" s="7" t="inlineStr">
         <is>
           <t>平日,祝日</t>
@@ -25152,9 +25112,7 @@
           <t>0853-23-7376</t>
         </is>
       </c>
-      <c r="G280" s="6" t="n">
-        <v>180</v>
-      </c>
+      <c r="G280" s="6" t="inlineStr"/>
       <c r="H280" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -25308,9 +25266,7 @@
           <t>0853-53-3330</t>
         </is>
       </c>
-      <c r="G283" s="6" t="n">
-        <v>160</v>
-      </c>
+      <c r="G283" s="6" t="inlineStr"/>
       <c r="H283" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -25414,9 +25370,7 @@
           <t>0853-25-7038</t>
         </is>
       </c>
-      <c r="G285" s="6" t="n">
-        <v>50</v>
-      </c>
+      <c r="G285" s="6" t="inlineStr"/>
       <c r="H285" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -25616,9 +25570,7 @@
           <t>0853-25-8782</t>
         </is>
       </c>
-      <c r="G289" s="6" t="n">
-        <v>240</v>
-      </c>
+      <c r="G289" s="6" t="inlineStr"/>
       <c r="H289" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -25668,9 +25620,7 @@
           <t>050-3535-6724</t>
         </is>
       </c>
-      <c r="G290" s="6" t="n">
-        <v>5</v>
-      </c>
+      <c r="G290" s="6" t="inlineStr"/>
       <c r="H290" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -25724,9 +25674,7 @@
           <t>０８５３－２８－３６６７</t>
         </is>
       </c>
-      <c r="G291" s="6" t="n">
-        <v>5</v>
-      </c>
+      <c r="G291" s="6" t="inlineStr"/>
       <c r="H291" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,日曜日,祝日</t>
@@ -25776,9 +25724,7 @@
           <t>0853-77-9841</t>
         </is>
       </c>
-      <c r="G292" s="6" t="n">
-        <v>80</v>
-      </c>
+      <c r="G292" s="6" t="inlineStr"/>
       <c r="H292" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -25878,9 +25824,7 @@
           <t>0853-62-9114</t>
         </is>
       </c>
-      <c r="G294" s="6" t="n">
-        <v>40</v>
-      </c>
+      <c r="G294" s="6" t="inlineStr"/>
       <c r="H294" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -26038,9 +25982,7 @@
           <t>0853-31-9447</t>
         </is>
       </c>
-      <c r="G297" s="6" t="n">
-        <v>35</v>
-      </c>
+      <c r="G297" s="6" t="inlineStr"/>
       <c r="H297" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -26194,9 +26136,7 @@
           <t>0853-27-9737</t>
         </is>
       </c>
-      <c r="G300" s="6" t="n">
-        <v>59</v>
-      </c>
+      <c r="G300" s="6" t="inlineStr"/>
       <c r="H300" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -26346,9 +26286,7 @@
           <t>0853－31－5988</t>
         </is>
       </c>
-      <c r="G303" s="6" t="n">
-        <v>50</v>
-      </c>
+      <c r="G303" s="6" t="inlineStr"/>
       <c r="H303" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -26398,9 +26336,7 @@
           <t>0853-20-7497</t>
         </is>
       </c>
-      <c r="G304" s="6" t="n">
-        <v>120</v>
-      </c>
+      <c r="G304" s="6" t="inlineStr"/>
       <c r="H304" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -26766,9 +26702,7 @@
           <t>0853-24-8515</t>
         </is>
       </c>
-      <c r="G311" s="6" t="n">
-        <v>20</v>
-      </c>
+      <c r="G311" s="6" t="inlineStr"/>
       <c r="H311" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -26872,9 +26806,7 @@
           <t>0853-72-5192</t>
         </is>
       </c>
-      <c r="G313" s="6" t="n">
-        <v>161</v>
-      </c>
+      <c r="G313" s="6" t="inlineStr"/>
       <c r="H313" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,祝日</t>
@@ -27190,9 +27122,7 @@
           <t>0853-24-9913</t>
         </is>
       </c>
-      <c r="G319" s="6" t="n">
-        <v>5</v>
-      </c>
+      <c r="G319" s="6" t="inlineStr"/>
       <c r="H319" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -27242,9 +27172,7 @@
           <t>０５０−３１７４−７１２２</t>
         </is>
       </c>
-      <c r="G320" s="6" t="n">
-        <v>5</v>
-      </c>
+      <c r="G320" s="6" t="inlineStr"/>
       <c r="H320" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -27826,9 +27754,7 @@
           <t>0853-21-2810</t>
         </is>
       </c>
-      <c r="G331" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G331" s="6" t="inlineStr"/>
       <c r="H331" s="7" t="inlineStr">
         <is>
           <t>平日</t>
@@ -27878,9 +27804,7 @@
           <t>0853-21-2880</t>
         </is>
       </c>
-      <c r="G332" s="6" t="n">
-        <v>20</v>
-      </c>
+      <c r="G332" s="6" t="inlineStr"/>
       <c r="H332" s="7" t="inlineStr">
         <is>
           <t>平日</t>
